--- a/신고신저가_20260821.xlsx
+++ b/신고신저가_20260821.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 미 재무부가 장기 국채 바이백을 두 배로 늘리자 장기금리가 무너졌고, 그렇게 풀린 온기는 주식이 아니라 금으로 갔다. 금값이 두 달 만의 최고인 4,530달러 부근까지 오르면서 미국·일본·홍콩·중국 네 시장에서 동시에 금광주가 신고가를 냈고, 반대로 뉴욕 3대 지수는 월마트 급락과 반도체 약세에 눌려 나란히 하락했다. 금리가 내렸는데도 주식이 못 오른 것은 금리 하락의 이유가 물가 안정이 아니라 채권시장 불안에 대한 당국 개입이었기 때문으로 추정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/20): 지수는 내렸지만 시장의 폭은 오히려 넓어졌다. S&amp;P500이 0.87퍼센트 빠지는 동안 신고가가 90종목으로 신저가 35종목을 크게 앞섰는데, 지수를 끌어내린 것이 소수의 대형주였다는 뜻이다. 실제로 월마트가 실적과 연간 전망을 모두 올리고도 9.2퍼센트 급락해 지수 셋을 함께 눌렀고, 반도체가 속한 전자기술 업종이 신저가 6종목으로 가장 약했다. 반면 에너지는 신고가 19종목으로 압도적이었고 코노코필립스를 비롯한 셰일 3사가 나란히 52주 고점을 새로 썼다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/20): 전날 3퍼센트 넘게 밀렸던 시장이 업종 전반에서 되돌림에 성공했다. 17개 업종지수가 모두 올랐고 그중 자동차가 5.0퍼센트로 가장 강했는데, 미 장기금리 급락이 할부금융 부담을 덜어준다는 해석이 혼다의 연중 최고가로 이어졌다. 스미토모금속광산은 금과 구리 동반 강세를 타고 10.8퍼센트 뛰며 상장 이래 최고가를 경신했다. 간사이전력은 기업용 전기요금 인상 발표가 곧바로 이익 기대로 연결되며 8.4퍼센트 올랐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/20): 제약과 금광이라는 두 축이 지수를 밀어올렸다. 항셍지수가 0.8퍼센트 오른 가운데 신고가 24종목 가운데 헬스케어가 8종목으로 가장 많았고, 중국생물제약이 상반기 순이익 92퍼센트 증가를 앞세워 12.5퍼센트 급등했다. 같은 업종에서 장쑤헝루이제약만은 매출과 이익이 함께 줄었다는 발표에 9.6퍼센트 빠졌는데, 업종 순풍이 실적을 대신해주지는 않는다는 점을 보여준다. 금광 쪽에서는 쯔진황금궈지가 11.3퍼센트 오르며 네 종목이 함께 신고가에 들었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/20): 상해종합이 0.24퍼센트 오르는 데 그쳤지만 그 안의 방향은 분명했다. 신고가는 은행 6종목과 비철금속 4종목에 몰린 반면, 신저가는 하이광정보와 캄브리콘 같은 AI 반도체 설계사에서 나왔다. 금값에 연동된 금광주가 츠펑지룽황금을 필두로 무더기 신고가를 낸 사이 반도체 상장지수펀드는 한 달 새 9.8퍼센트 빠지며 연초 이후 쌓은 상승분을 되돌리고 있다. 실적 발표를 앞둔 닝보은행이 3.6퍼센트 오른 데서 보듯 자금은 배당과 안전자산 쪽으로 기울었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ① 금값이 4,500달러대를 지켜내는지 살펴야 한다. 재무부 바이백이 일회성 개입에 그치면 금리도 금값도 되돌릴 수 있다. ② 월마트의 가격 인하 선언이 다른 소매업체의 마진 전망으로 번지는지, 딕스스포팅굿즈의 동반 신저가가 그 첫 신호인지 확인할 필요가 있다. ③ 미국 전자기술과 중국 AI 반도체가 같은 날 함께 약했던 것이 단순한 차익실현인지, AI 하드웨어 눈높이 조정의 시작인지 가려봐야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 네 나라에서 같은 날 금광주가 동시에 신고가를 낸 로직은 끝까지 따라가 볼 만하다. 재료는 미 재무부의 장기물 국채 바이백 확대였고, 이것이 장기금리를 끌어내리면서 이자를 주지 않는 금의 기회비용을 낮췄다. 여기까지가 금 자체의 멀티플 경로라면, 금광주가 금보다 훨씬 크게 오른 이유는 이익 경로에 있다. 금광회사의 판매가격은 금값을 그대로 따라가는데 채굴원가는 단기적으로 거의 고정돼 있어서, 금값 상승분이 대부분 마진에 그대로 얹힌다. 금값이 몇 퍼센트 오를 때 금광주가 두 자릿수로 뛰는 것은 이 원가 고정성 때문이다. 같은 재료가 반대로 작동한 짝도 함께 나왔는데, 금리 하락은 혼다처럼 할부금융에 기대는 업종에는 연료였지만 뉴욕 지수 전체에는 약이 되지 못했다. 이 논리가 맞는지는 금광업체들의 다음 분기 실현 판매가격과 채굴원가 격차가 실제로 벌어지는지로 확인할 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 미국은 8월 20일 정규장 마감분으로 한국시간 8월 21일 새벽 5시에 끝난 세션이다. 일본·홍콩·중국A는 8월 20일 종가 기준이며 8월 21일 장은 아직 열리지 않았다. 닛케이지수 수치만 수집 시점 문제로 8월 19일자가 들어와 있어, 일본 서술은 8월 20일 업종지수 등락을 근거로 했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +791,19 @@
       <c r="C2" t="n">
         <v>7641.16</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.87</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>-2.02</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>11.62</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +829,19 @@
       <c r="C3" t="n">
         <v>26067.17</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>-2.75</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>1.46</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>-0.77</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>12.16</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +867,19 @@
       <c r="C4" t="n">
         <v>6471.17</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>-5.8</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>1.98</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-13.9</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>53.56</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +905,19 @@
       <c r="C5" t="n">
         <v>65326.42</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="4" t="n">
         <v>-3.16</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>-3.25</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>1.85</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>9.23</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>29.77</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +943,19 @@
       <c r="C6" t="n">
         <v>3903.72</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.24</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>-0.59</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>0.95</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-5.09</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>-1.64</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +981,19 @@
       <c r="C7" t="n">
         <v>4592.75</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>-1.53</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>-2.64</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-5.21</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>-0.8</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1019,19 @@
       <c r="C8" t="n">
         <v>25698.49</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>1.19</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>3.24</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>0.18</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>0.27</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1057,19 @@
       <c r="C9" t="n">
         <v>4700.53</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>0.39</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>-1.92</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>-3.56</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-14.78</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1188,7 @@
       <c r="F2" t="n">
         <v>19</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1229,7 @@
       <c r="F3" t="n">
         <v>13</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1270,7 @@
       <c r="F4" t="n">
         <v>13</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1311,7 @@
       <c r="F5" t="n">
         <v>12</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1352,7 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1393,7 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1434,7 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1475,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1516,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1557,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1598,7 @@
       <c r="F12" t="n">
         <v>-1</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1557,7 +1639,7 @@
       <c r="F13" t="n">
         <v>-2</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1598,7 +1680,7 @@
       <c r="F14" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1639,7 +1721,7 @@
       <c r="F15" t="n">
         <v>-4</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1680,7 +1762,7 @@
       <c r="F16" t="n">
         <v>-6</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +2006,7 @@
       <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2047,7 @@
       <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2004,7 +2086,7 @@
       <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2045,7 +2127,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2084,7 +2166,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2123,7 +2205,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2162,7 +2244,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2201,7 +2283,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2240,7 +2322,7 @@
       <c r="F30" t="n">
         <v>-1</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2677,7 +2759,7 @@
       <c r="F41" t="n">
         <v>7</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2800,7 @@
       <c r="F42" t="n">
         <v>5</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2759,7 +2841,7 @@
       <c r="F43" t="n">
         <v>3</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2800,7 +2882,7 @@
       <c r="F44" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2839,7 +2921,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2880,7 +2962,7 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2919,7 +3001,7 @@
       <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3393,7 +3475,7 @@
       <c r="F59" t="n">
         <v>6</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3434,7 +3516,7 @@
       <c r="F60" t="n">
         <v>4</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3475,7 +3557,7 @@
       <c r="F61" t="n">
         <v>2</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3516,7 +3598,7 @@
       <c r="F62" t="n">
         <v>2</v>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3555,7 +3637,7 @@
       <c r="F63" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3594,7 +3676,7 @@
       <c r="F64" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3635,7 +3717,7 @@
       <c r="F65" t="n">
         <v>-1</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3676,7 +3758,7 @@
       <c r="F66" t="n">
         <v>-2</v>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4099,30 +4181,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4143,90 +4226,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4248,58 +4336,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>소프트웨어는 순강도 13으로 강했지만 반도체 약세가 상쇄해 0.3% 하락, 주간 4.0% 조정</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4319,58 +4412,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>1.9%로 낙폭 최대이나 생명과학 도구주는 신고가 16종목. 대형 제약·보험이 지수를 눌렀다</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4390,58 +4488,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>은행주 차익실현에 0.9% 하락, 다만 3개월 10.6%로 중기 추세는 상위권 유지</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4461,58 +4564,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>월마트발 소비 둔화 우려로 1.6% 하락, 딕스스포팅굿즈 등 소매 신저가 3종목</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4532,58 +4640,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>특별한 촉매 없이 하락, 연초 이후 5.4% 마이너스로 11개 업종 중 최하위 유지</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4603,58 +4716,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>제조업 신저가 6종목으로 약세, 노드슨 실적 서프라이즈에도 업종 전반은 되밀림</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4674,58 +4792,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>월마트 9.2% 급락 여파가 필수소비재 전반으로 번지며 1.4% 하락</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4745,58 +4868,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>유가 강세로 유일하게 상승. 에너지 순강도 19로 전 업종 최고, 셰일 3사 52주 신고가</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>44.6</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4816,58 +4944,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>금리 하락에도 반등 못하고 하락, 신저가 3종목으로 순강도 마이너스 전환</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4887,58 +5020,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>금·구리 강세로 비에너지광물 순강도 12를 기록했으나 ETF는 화학 비중에 눌려 약보합</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4958,58 +5096,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>장기금리 급락에 조달비용 부담이 줄며 소폭 상승, 3개월 수익률은 여전히 부진</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5029,58 +5172,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5100,58 +5244,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>8</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5171,58 +5316,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>12</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5242,58 +5388,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5313,58 +5460,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>8.4</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>11</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5384,58 +5532,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5455,58 +5604,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>48.4</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5526,58 +5676,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>7</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5597,58 +5748,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>31.5</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5668,58 +5820,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>13.6</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5739,58 +5892,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5810,58 +5964,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>13</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5881,58 +6036,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5952,58 +6108,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6023,58 +6180,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>-5.7</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>42.1</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6094,58 +6252,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6165,58 +6324,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-5.7</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-5.5</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6236,58 +6396,63 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>제약과 금광 두 축이 지수를 끌어올리며 0.8% 상승, 신고가 24종목</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-14.4</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6307,58 +6472,63 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>본토 은행·금광 강세를 그대로 반영해 1.4% 상승, 홍콩 3개 ETF 중 최고</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-17.8</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6378,56 +6548,61 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>콰이서우 11.0% 급락 등 플랫폼 약세로 0.1% 강보합에 그침</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-14.5</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6445,58 +6620,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>하이광정보·캄브리콘 신저가로 0.6% 하락, 한 달 9.8% 조정으로 낙폭 최대</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>-5.1</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6516,58 +6696,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>AI 반도체 약세에 동반 하락, 한 달 7.1% 조정에도 연초 이후 27.0%는 유지</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-7.1</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6587,58 +6772,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>1.1%로 A주 상승률 1위이나 개별 촉매는 확인되지 않아 수급 반등으로 추정</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-11.3</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6658,56 +6848,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>0.7% 하락, 3개월 21.2% 조정 지속으로 전기차 밸류체인 약세가 길어지고 있다</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-21.2</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6725,58 +6920,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>1.0% 하락으로 A주 최약. 3개월 19.2% 조정이 이어지며 반등 신호 부재</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-19.2</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-20.1</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6796,56 +6996,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>0.5% 반등했으나 3개월 23.6% 하락으로 A주 업종 중 낙폭 최대 구간에 머물러 있다</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-23.6</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-11.7</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6863,58 +7068,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>0.2% 강보합에 그침, 주간 5.1% 하락으로 소비 회복 신호는 아직 확인되지 않는다</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-5.1</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-20.5</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6934,58 +7144,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>은행 신고가 6종목으로 A주 최강 업종. 실적 시즌 앞두고 배당 선호 자금 유입</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7005,58 +7220,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>금값 급등에 금광주 무더기 신고가, 비철금속 순강도 4로 A주 상위권</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-6.7</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>6</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7076,58 +7296,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>금리 하락 기대에 0.9% 반등, 다만 연초 이후 18.7% 마이너스로 낙폭은 여전히 최대</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-11.2</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-18.7</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>11</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7147,58 +7372,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>거래대금 부진 속 0.1% 보합, 한 달 4.6% 하락으로 지수 정체를 그대로 반영</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7218,58 +7448,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>위탁개발 업종 강세로 1.0% 상승, 우시앱텍·파마론 나란히 신고가</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7289,58 +7524,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>소비 관련 뚜렷한 촉매 없이 0.8% 반등, 3개월 기준으로는 약세 지속</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-15.6</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7352,7 +7592,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1.9"/>
@@ -7364,7 +7604,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-5.9"/>
@@ -7376,7 +7616,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-9.800000000000001"/>
@@ -7388,7 +7628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-23.6"/>
@@ -7400,7 +7640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-20.5"/>
@@ -7412,7 +7652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7424,7 +7664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7436,7 +7676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7448,7 +7688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7460,7 +7700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7472,7 +7712,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7586,12 +7826,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7635,10 +7875,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>(대형마트 소매유통) 실적 상회·연간 상향에도 미국 동일점포 2.6%와 3분기 이익 가이던스 부진</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7687,14 +7931,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 엑손모빌(석유·가스 통합메이저): 이란 긴장으로 브렌트 90달러, 유가 강세 직접 수혜</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7743,15 +7987,15 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7799,10 +8043,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7851,15 +8095,15 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7903,15 +8147,15 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7955,10 +8199,10 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8011,10 +8255,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>(셰일 원유·가스 개발) 유가 강세와 2분기 실적 호조로 52주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8063,10 +8311,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8113,14 +8361,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) TJX컴퍼니스(TJ맥스 등 오프프라이스 유통): 2분기 호실적에도 3분기 EPS 가이던스 컨센 하회</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8169,10 +8417,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8221,15 +8469,15 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8273,10 +8521,10 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8325,10 +8573,10 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8377,14 +8625,14 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) 아그니코이글마인스(금 채굴): 달러 약세와 장기금리 반락으로 금값 급등 수혜</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8433,15 +8681,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8489,10 +8737,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8541,15 +8789,15 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8597,15 +8845,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8649,10 +8897,10 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8705,10 +8953,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8757,10 +9005,10 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8809,10 +9057,10 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8861,10 +9109,10 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8917,10 +9165,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8973,10 +9221,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>(셰일 원유·가스 개발) 유가 강세에 E&amp;P 업종 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9025,10 +9277,10 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9077,10 +9329,10 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9129,10 +9381,10 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9181,15 +9433,15 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9231,15 +9483,15 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9287,15 +9539,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9343,10 +9595,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9395,10 +9647,10 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9451,14 +9703,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr">
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>(전일) 세노버스에너지(캐나다 석유·가스 통합기업): 이란·호르무즈 리스크發 유가 강세 수혜</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9511,10 +9763,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>(퍼미안 셰일 원유) 유가 강세에 E&amp;P 업종 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9563,15 +9819,15 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9615,10 +9871,10 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9667,10 +9923,10 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9719,15 +9975,15 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9771,10 +10027,10 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="8" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9827,14 +10083,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N43" s="8" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>(전일) 벡톤디킨슨(주사기·진단 등 의료기기): 개별 뉴스 없음, 헬스케어 랠리 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9883,10 +10139,10 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9935,15 +10191,15 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9987,10 +10243,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10037,14 +10293,14 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>(전일) 아틀라시안(협업 소프트웨어): 4분기 실적 서프라이즈에 BofA 등 목표주가 대거 상향</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10093,15 +10349,15 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10149,10 +10405,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="8" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10201,15 +10457,15 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10257,15 +10513,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10309,10 +10565,10 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10361,15 +10617,15 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="8" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10417,15 +10673,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10469,10 +10725,14 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr">
+        <is>
+          <t>(금 채굴) 금값 2개월래 최고 4530달러 부근, 금광주 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10521,10 +10781,10 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10573,10 +10833,10 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="8" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10629,10 +10889,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="8" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10681,10 +10941,10 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10733,15 +10993,15 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="8" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10789,15 +11049,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr">
+        <is>
+          <t>(유전체 시퀀싱 장비) 2분기 매출 서프라이즈 여진에 신고가 지속</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10841,15 +11105,15 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="8" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10893,10 +11157,10 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10945,10 +11209,10 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11001,10 +11265,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11057,15 +11321,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11109,15 +11373,15 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11161,10 +11425,10 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11213,14 +11477,14 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr">
+      <c r="N69" s="10" t="inlineStr">
         <is>
           <t>(전일) 커티스라이트(방산·원자력 부품): 특별한 뉴스 없음(8월 실적 이후 밸류에이션 조정 지속)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11269,15 +11533,15 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11319,10 +11583,10 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="8" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11371,14 +11635,14 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="8" t="inlineStr">
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>(전일) 코어마이닝(금·은 채굴): 금 4.8%·은 4.8% 급등에 신고가 경신</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11427,10 +11691,10 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="8" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11477,10 +11741,10 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="8" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11529,15 +11793,15 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" s="8" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11579,10 +11843,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N76" s="8" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11635,19 +11899,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N77" s="8" t="inlineStr">
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>(전일) 퍼미안리소시스(셰일 원유 생산): 웰스파고 목표주가 상향(26→27달러)에 유가 강세 동반</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11691,15 +11955,15 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" s="8" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11745,10 +12009,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="8" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>(산업용 접착·도포장비) 3분기 EPS 3.25달러로 컨센 상회, 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11801,15 +12069,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N80" s="8" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11853,10 +12121,10 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="8" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11909,10 +12177,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N82" s="8" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr">
+        <is>
+          <t>(스포츠용품 소매) 월마트발 소비 둔화 우려 전이로 동반 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11961,10 +12233,10 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12013,15 +12285,15 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" s="8" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12065,15 +12337,15 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" s="8" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12115,10 +12387,10 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12167,15 +12439,15 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" s="8" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12219,15 +12491,15 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" s="8" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12275,10 +12547,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N89" s="8" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12327,19 +12599,19 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" s="8" t="inlineStr">
+      <c r="N90" s="10" t="inlineStr">
         <is>
           <t>(전일) 헤클라마이닝(은 채굴): 금리인상 우려 후퇴로 금·은값 급등, 광산주 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12387,10 +12659,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N91" s="8" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12443,10 +12715,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N92" s="8" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12497,15 +12769,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N93" s="8" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12543,15 +12815,15 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" s="8" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12597,15 +12869,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N95" s="8" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr">
+        <is>
+          <t>(건축자재 유통) 특별한 뉴스 없음, 차입 인수 부담 우려 지속 추정</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12649,15 +12925,15 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12701,15 +12977,19 @@
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" s="8" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr">
+        <is>
+          <t>(태양광 트래커·에너지저장) 실적 부진과 목표주가 하향 여진 추정</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12753,15 +13033,15 @@
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" s="8" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12807,10 +13087,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N99" s="8" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr">
+        <is>
+          <t>(산업용 송풍·공조장비) 51억유로 규모 인수 자금조달 부담 우려로 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12863,14 +13147,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N100" s="8" t="inlineStr">
+      <c r="N100" s="10" t="inlineStr">
         <is>
           <t>(전일) 왓츠코(냉난방공조 유통): 30년물 금리 2007년래 최고에 주택·건자재 수요 우려 확산</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12917,10 +13201,10 @@
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" s="8" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12973,10 +13257,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N102" s="8" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13025,10 +13309,10 @@
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" s="8" t="inlineStr"/>
+      <c r="N103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13075,15 +13359,15 @@
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" s="8" t="inlineStr"/>
+      <c r="N104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13129,15 +13413,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N105" s="8" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13181,15 +13465,15 @@
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" s="8" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13229,15 +13513,19 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="8" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr">
+        <is>
+          <t>(AI 정밀의료 데이터분석) 특별한 뉴스 없음, AI헬스케어 순환매 유입 추정</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13285,10 +13573,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N108" s="8" t="inlineStr"/>
+      <c r="N108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13337,15 +13625,15 @@
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" s="8" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13389,15 +13677,15 @@
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" s="8" t="inlineStr"/>
+      <c r="N110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13441,15 +13729,15 @@
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" s="8" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13491,10 +13779,10 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" s="8" t="inlineStr"/>
+      <c r="N112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13543,10 +13831,10 @@
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" s="8" t="inlineStr"/>
+      <c r="N113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="A114" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13593,19 +13881,19 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" s="8" t="inlineStr">
+      <c r="N114" s="10" t="inlineStr">
         <is>
           <t>(전일) 인라이트리뉴어블(태양광·풍력 발전 개발): 특별한 뉴스 없음(밸류에이션 부담·차익실현 추정)</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="inlineStr">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13649,10 +13937,10 @@
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" s="8" t="inlineStr"/>
+      <c r="N115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13701,15 +13989,15 @@
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" s="8" t="inlineStr"/>
+      <c r="N116" s="10" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13751,10 +14039,14 @@
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" s="8" t="inlineStr"/>
+      <c r="N117" s="10" t="inlineStr">
+        <is>
+          <t>(중추신경계 치료제) 증권사 목표주가 하향 등 실적 우려 지속</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13805,10 +14097,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N118" s="8" t="inlineStr"/>
+      <c r="N118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13861,14 +14153,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N119" s="8" t="inlineStr">
+      <c r="N119" s="10" t="inlineStr">
         <is>
           <t>(전일) 달링인그리디언츠(동물부산물·재생연료 원료): 2분기 사상최대 실적·자사주 10억달러 여진</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13917,10 +14209,10 @@
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" s="8" t="inlineStr"/>
+      <c r="N120" s="10" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13969,15 +14261,15 @@
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" s="8" t="inlineStr"/>
+      <c r="N121" s="10" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14021,15 +14313,15 @@
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" s="8" t="inlineStr"/>
+      <c r="N122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14077,10 +14369,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N123" s="8" t="inlineStr"/>
+      <c r="N123" s="10" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14129,15 +14421,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N124" s="8" t="inlineStr"/>
+      <c r="N124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14185,15 +14477,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N125" s="8" t="inlineStr"/>
+      <c r="N125" s="10" t="inlineStr">
+        <is>
+          <t>(생명과학 진단·시약) 2분기 EPS 2.62달러로 컨센 상회</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="inlineStr">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14237,7 +14533,7 @@
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" s="8" t="inlineStr"/>
+      <c r="N126" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N126"/>
@@ -14343,7 +14639,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14394,19 +14690,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 혼다(자동차·이륜차 제조): 개별 뉴스 없음, 신고가권에서 차익실현 매도</t>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>(자동차 제조) 미 장기금리 급락에 할부금융 우려 완화, 7월 수출 호조</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14450,15 +14746,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>(종합금융·리스) 특별한 뉴스 없음, 반등장에서 소외되며 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14500,15 +14800,15 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14550,15 +14850,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>(제약) 특별한 뉴스 없음, 반등장 속 방어주 순환매 추정</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14604,15 +14908,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>(완구·게임·엔터테인먼트) 1분기 영업이익 33% 증가, 실적 전망 상향</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14658,15 +14966,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>(포털·핀테크 플랫폼) 페이페이 결제액 34.9% 성장 등 실적 호조 지속</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14710,15 +15022,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>(비철금속 제련·금은동 광업) 금·구리 급등에 상장 이래 최고가 경신</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14760,10 +15076,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>(전력·원전 운영) 기업용 전기요금 10~15% 인상 발표로 실적 개선 기대</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14812,10 +15132,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14866,19 +15186,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 올림푸스(내시경 등 의료기기): 실적 회복 기대와 자사주 매입 확대로 매수세 지속</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14920,15 +15240,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14974,7 +15294,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N13"/>
@@ -15080,12 +15400,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15131,15 +15451,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15183,15 +15503,15 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15233,15 +15553,15 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15289,15 +15609,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>(제약) 상반기 매출 1.9%·조정순이익 12.7% 감소로 업종과 반대로 급락</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15339,10 +15663,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴) 미 재무부 국채 바이백 확대에 금리 급락, 금값 급등</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15395,14 +15723,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 비원메디슨즈(항암 신약 개발): 상반기 순이익 386% 급증 등 실적 호조</t>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>(항암 신약) 혁신신약 업종 전반 강세에 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15455,14 +15783,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 코스코해운홀딩스(컨테이너 해운): 특별한 뉴스 없음(호르무즈발 운임 강세 지속 추정)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15515,14 +15843,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 우시바이오로직스(바이오의약품 위탁개발생산): 신약목록 편입 기대에 업종 상승률 선두</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15571,14 +15899,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 이노벤트바이오로직스(항체 신약 개발): 개별 뉴스 없음, 신약 섹터 강세에 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15629,19 +15957,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 콰이쇼우(중국 2위 숏폼동영상·라이브커머스): 전자상거래 거래액 성장 둔화 우려, 8/20 실적발표 앞두고 신저가</t>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>(숏폼 동영상) 2분기 조정순이익 30.3% 감소, AI 투자 부담 지속</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15681,15 +16009,19 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴) 금값 급등에 금광주 일제히 강세</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15727,10 +16059,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15777,19 +16109,19 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 스와이어프로퍼티스(홍콩 상업용 부동산): 씨티의 홍콩 소매경기 하반기 개선 전망 보고서</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15829,15 +16161,15 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15881,15 +16213,19 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>(택배 물류) 실적은 무난했으나 연간 물동량 가이던스 하향</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15929,15 +16265,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15981,10 +16317,10 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16033,19 +16369,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>(전일) SITC인터내셔널(아시아 역내 컨테이너 해운): 개별 뉴스 없음, 중간실적 앞둔 해운 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16091,15 +16427,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16143,15 +16479,15 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16193,10 +16529,14 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>(제약) 상반기 순이익 132~143% 증가 가이던스 발표 여진</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16249,10 +16589,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>(위탁연구개발) 혁신신약 업종 실적 호조에 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16303,15 +16647,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴) 금값 급등과 실적 호조 여진으로 52주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16353,15 +16701,15 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16405,15 +16753,15 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16455,15 +16803,19 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>(제약) 상반기 순이익 92% 급증, 기술수출 수익 21배 증가</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16507,10 +16859,14 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴) 금값 급등에 금광주 일제히 강세</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16559,7 +16915,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N29" s="8" t="inlineStr">
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국동방항공(항공운송): 중동 긴장발 유가 급등으로 항공유 비용 부담 확대</t>
         </is>
@@ -16669,12 +17025,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16718,15 +17074,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>(AI 반도체 설계) 보호예수 해제 물량 출회 우려로 하락</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16770,15 +17130,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>(AI 반도체 설계) 특별한 호재 부재, 차익실현과 수급 이탈 추정</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16824,10 +17188,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>(위탁연구개발) 미 바이오텍 지수 급등 여파로 위탁개발 업종 강세</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16872,19 +17240,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 중신은행(전국구 주식제 상업은행): 테크주 급락 자금이 저평가 고배당 은행으로 이동</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16928,10 +17296,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16980,19 +17348,19 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 코스코해운지주 A주(중국 최대 국영 컨테이너 해운): 호르무즈 운임 급등·머스크 가이던스 상향에 해운주 동반 급등</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17038,10 +17406,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17094,14 +17462,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 닝보은행(도시상업은행): 주력자금 순유입 지속, 저평가 고배당 방어주 로테이션 수혜</t>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>(지방은행) 상반기 실적발표를 앞두고 고배당·안전자산 선호 매수</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17150,19 +17518,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 화뎬신에너지(화뎬그룹 산하 신재생 발전사): 특별한 뉴스 없음(신재생 발전주 약세 흐름 속 신저가)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17206,10 +17574,10 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17258,14 +17626,14 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) 상하이은행(도시상업은행): 은행·배당 ETF 자금 유입 지속, 방어주 로테이션에 사상 최고가</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17312,19 +17680,19 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 산둥골드(중국 최대 금광기업): 국제 금값 급등과 안전자산 수요로 동반 상승</t>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴) 미 국채금리 하락발 금값 급등에 대표 금광주로 매수 집중</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17366,15 +17734,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17416,15 +17784,15 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17466,10 +17834,14 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴) 금값 4500달러대 진입에 귀금속주 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17516,10 +17888,10 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17566,15 +17938,15 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17616,10 +17988,10 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17668,19 +18040,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>(전일) 선전자리촹(PCB 제조, 8월 4일 신규 상장): 상장 초기 단타자금 이탈로 하한가</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17728,15 +18100,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>(위탁연구개발) 해외 항암 파이프라인 호재로 혁신신약 업종 급등</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17778,15 +18154,19 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴) 미 국채 바이백발 금리 급락에 금값 급등, 귀금속주 강세</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17828,10 +18208,14 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴) 달러 약세와 금값 급등에 연동한 귀금속 테마 상승</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17882,7 +18266,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr">
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국동방항공(항공 운송): 국제유가 상승에 따른 항공유 비용 부담과 시장 약세 동반</t>
         </is>
